--- a/Python/Hockey pool/2025/My Predictions2025.xlsx
+++ b/Python/Hockey pool/2025/My Predictions2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abrig\Documents\Coding_Practice\Python\Hockey pool\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E16C86-7369-4A56-A548-C56F2AEDEB2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA70D42E-5047-4626-88BE-E1F9D006B9C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{CCC5B65E-930E-4DB7-8BD5-D516C728EBC5}"/>
+    <workbookView xWindow="-28920" yWindow="-1740" windowWidth="29040" windowHeight="15840" xr2:uid="{CCC5B65E-930E-4DB7-8BD5-D516C728EBC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="192">
   <si>
     <t>DATE</t>
   </si>
@@ -16136,6 +16136,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{819ACA58-DCD7-4A09-9052-0851D3ECB0FF}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:CM95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -27481,125 +27482,128 @@
       <c r="AA59" s="1" t="s">
         <v>187</v>
       </c>
+      <c r="AI59" t="s">
+        <v>35</v>
+      </c>
       <c r="AJ59">
         <f>COUNTIFS($L$2:$L$106, AI59, $E$2:$E$106, 1) + COUNTIFS($M$2:$M$106, AI59, $E$2:$E$106, 1)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK59">
         <f>COUNTIFS($L$2:$L$106, AI59, $E$2:$E$106, 2) + COUNTIFS($M$2:$M$106, AI59, $E$2:$E$106, 2)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AL59">
         <f>COUNTIFS($L$2:$L$106, AI59, $E$2:$E$106, 3) + COUNTIFS($M$2:$M$106, AI59, $E$2:$E$106, 3)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM59">
         <f>COUNTIFS($L$2:$L$106, AI59, $E$2:$E$106, 4) + COUNTIFS($M$2:$M$106, AI59, $E$2:$E$106, 4)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AN59">
         <f>AJ59+AK59+AL59+AM59</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AO59">
         <f>COUNTIF($M$2:$M$106, AI59)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AP59">
         <f>COUNTIF($L$2:$L$106, AI59)</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AQ59">
         <f>AS59+AU59</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AR59">
         <f>AN59-AQ59</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AS59">
         <f>SUMPRODUCT(($M$2:$M$106=AI59)*($T$2:$T$106&gt;$S$2:$S$106))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AT59">
         <f>SUMPRODUCT(($M$2:$M$106=AI59)*($T$2:$T$106&lt;$S$2:$S$106))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU59">
         <f>SUMPRODUCT(($L$2:$L$106=AI59)*($T$2:$T$106&lt;$S$2:$S$106))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AV59">
         <f>SUMPRODUCT(($L$2:$L$106=AI59)*($T$2:$T$106&gt;$S$2:$S$106))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW59">
         <f>COUNTIFS($M$2:$M$106,AI59,$E$2:$E$106,4)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AX59">
         <f>COUNTIFS($L$2:$L$106,AI59,$E$2:$E$106,4)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AY59">
         <f>SUMIFS($T$2:$T$106, $M$2:$M$106, AI59,$E$2:$E$106, 4)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AZ59">
         <f>SUMIFS($S$2:$S$106, $L$2:$L$106, AI59,$E$2:$E$106, 4)</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BA59">
         <f>SUMIFS($S$2:$S$106, $M$2:$M$106, AI59,$E$2:$E$106, 4)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BB59">
         <f>SUMIFS($T$2:$T$106, $L$2:$L$106, AI59,$E$2:$E$106, 4)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BC59">
         <f t="shared" ref="BC59:BD60" si="95">AY59-BA59</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BD59">
         <f t="shared" si="95"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE59">
         <f>AY59+AZ59</f>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BF59">
         <f>BA59+BB59</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BG59">
         <f>(AY59+AZ59)-(BA59+BB59)</f>
-        <v>0</v>
-      </c>
-      <c r="BH59" t="e">
+        <v>11</v>
+      </c>
+      <c r="BH59">
         <f t="shared" ref="BH59:BI60" si="96">AY59/AW59</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BI59" t="e">
+        <v>5</v>
+      </c>
+      <c r="BI59">
         <f t="shared" si="96"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BJ59" t="e">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="BJ59">
         <f t="shared" ref="BJ59:BK60" si="97">BA59/AW59</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BK59" t="e">
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="BK59">
         <f t="shared" si="97"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL59" t="e">
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="BL59">
         <f>BE59/AJ59</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM59" t="e">
+        <v>5.6</v>
+      </c>
+      <c r="BM59">
         <f>BF59/AJ59</f>
-        <v>#DIV/0!</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="60" spans="1:65" x14ac:dyDescent="0.25">
@@ -27688,125 +27692,128 @@
         <f>IF(ISBLANK(Table2[[#This Row],[GAMENUM]]), " ", IF((Table2[[#This Row],[TOPSEEDWINS]]+Table2[[#This Row],[LOWSEEDWINS]]) &lt;&gt; Table2[[#This Row],[GAMENUM]], 0, 1))</f>
         <v>1</v>
       </c>
+      <c r="AI60" t="s">
+        <v>52</v>
+      </c>
       <c r="AJ60">
         <f>COUNTIFS($L$2:$L$106, AI60, $E$2:$E$106, 1) + COUNTIFS($M$2:$M$106, AI60, $E$2:$E$106, 1)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AK60">
         <f>COUNTIFS($L$2:$L$106, AI60, $E$2:$E$106, 2) + COUNTIFS($M$2:$M$106, AI60, $E$2:$E$106, 2)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL60">
         <f>COUNTIFS($L$2:$L$106, AI60, $E$2:$E$106, 3) + COUNTIFS($M$2:$M$106, AI60, $E$2:$E$106, 3)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM60">
         <f>COUNTIFS($L$2:$L$106, AI60, $E$2:$E$106, 4) + COUNTIFS($M$2:$M$106, AI60, $E$2:$E$106, 4)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AN60">
         <f t="shared" ref="AN60" si="98">AJ60+AK60+AL60+AM60</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AO60">
         <f>COUNTIF($M$2:$M$106, AI60)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AP60">
         <f>COUNTIF($L$2:$L$106, AI60)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ60">
         <f>AS60+AU60</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AR60">
         <f>AN60-AQ60</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AS60">
         <f>SUMPRODUCT(($M$2:$M$106=AI60)*($T$2:$T$106&gt;$S$2:$S$106))</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AT60">
         <f>SUMPRODUCT(($M$2:$M$106=AI60)*($T$2:$T$106&lt;$S$2:$S$106))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU60">
         <f>SUMPRODUCT(($L$2:$L$106=AI60)*($T$2:$T$106&lt;$S$2:$S$106))</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV60">
         <f>SUMPRODUCT(($L$2:$L$106=AI60)*($T$2:$T$106&gt;$S$2:$S$106))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AW60">
         <f>COUNTIFS($M$2:$M$106,AI60,$E$2:$E$106,4)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AX60">
         <f>COUNTIFS($L$2:$L$106,AI60,$E$2:$E$106,4)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AY60">
         <f>SUMIFS($T$2:$T$106, $M$2:$M$106, AI60,$E$2:$E$106, 4)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ60">
         <f>SUMIFS($S$2:$S$106, $L$2:$L$106, AI60,$E$2:$E$106, 4)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BA60">
         <f>SUMIFS($S$2:$S$106, $M$2:$M$106, AI60,$E$2:$E$106, 4)</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BB60">
         <f>SUMIFS($T$2:$T$106, $L$2:$L$106, AI60,$E$2:$E$106, 4)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BC60">
         <f t="shared" si="95"/>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="BD60">
         <f t="shared" si="95"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="BE60">
         <f t="shared" ref="BE60" si="99">AY60+AZ60</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BF60">
         <f t="shared" ref="BF60" si="100">BA60+BB60</f>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BG60">
         <f t="shared" ref="BG60" si="101">(AY60+AZ60)-(BA60+BB60)</f>
-        <v>0</v>
-      </c>
-      <c r="BH60" t="e">
+        <v>-11</v>
+      </c>
+      <c r="BH60">
         <f t="shared" si="96"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BI60" t="e">
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="BI60">
         <f t="shared" si="96"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BJ60" t="e">
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="BJ60">
         <f t="shared" si="97"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BK60" t="e">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="BK60">
         <f t="shared" si="97"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BL60" t="e">
+        <v>5</v>
+      </c>
+      <c r="BL60">
         <f t="shared" ref="BL60" si="102">BE60/AJ60</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BM60" t="e">
+        <v>2.8333333333333335</v>
+      </c>
+      <c r="BM60">
         <f t="shared" ref="BM60" si="103">BF60/AJ60</f>
-        <v>#DIV/0!</v>
+        <v>4.666666666666667</v>
       </c>
     </row>
     <row r="61" spans="1:65" x14ac:dyDescent="0.25">
